--- a/config/weather.xlsx
+++ b/config/weather.xlsx
@@ -1308,7 +1308,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>水属性速度上昇;火属性の味方のダメージが減少する。\n各ターン終了時、味方全員の一部の状態異常を解除する。</t>
+          <t>水属性速度提升；火属性伙伴的伤害减少。\n各回合结束时，解除我方全体人员一部分的异常状态。</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>雷属性ダメージ上昇\n各ターン終了時、雷を戦場のランダムな目標1体に落とし、大量ダメージを与える(雷属性の味方は一定の確率でそのダメージを吸収)。非雷属性の味方は一定の確率で【麻痺】状態になる。</t>
+          <t>雷属性伤害上升\n各回合结束时，将雷电落在战场上的一个随机目标上，造成大量伤害（雷属性的我方有一定概率吸收该伤害）。非雷属性的伙伴有一定概率会变成【麻痹】状态。</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>氷属性の特防·物防上昇\n全ての非氷属性の味方は各ターン終了時、一定の氷元素ダメージを受け、一定の確率で【凍結】状態になる。</t>
+          <t>冰属性的特防·物防上升\n所有非冰属性的伙伴各回合结束时，受到一定的冰元素伤害，有一定概率进入【冻结】状态。</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>砂嵐</t>
+          <t>沙尘暴</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>岩属性の物理防御上昇\n全ての非陸属性と岩属性の味方は各ターン終了時、一定の確率で【暗闇】状態になる。</t>
+          <t>岩石属性的物理防御上升\n所有非陆地属性和岩石属性的我方各回合结束时，有一定概率进入【黑暗】状态。</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>乱気流</t>
+          <t>湍流</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>空属性速度上昇\n各ターン終了時、各味方は一定の確率で【断絶】され、非空属性の味方は地面に落ちた際に一定のHPを失う。</t>
+          <t>空属性速度上升\n各回合结束时，各我方有一定的概率被【断绝】，非空属性的我方落地时会失去一定的HP。</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>火属性ダメージ上昇;水属性の味方のダメージが減少する。\n味方全員が【太陽の力】を獲得する(毎ターン一定のHPを消失、ダメージ上昇、重複可能)。</t>
+          <t>火属性伤害上升；水属性伙伴的伤害减少。\n我方全员获得【太阳之力】（每回合一定的HP消失，伤害上升，可重复）。</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1810,14 +1810,14 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>大雾</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>濃霧</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>濃霧</t>
-        </is>
-      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>Thick fog</t>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>全員の命中率が大幅減少</t>
+          <t>全员命中率大幅降低</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>非闇属性、邪属性ダメージ減少；\n闇属性の特攻ダメージを無効にする；\n闇属性のスキル耐性が大幅に増加する。</t>
+          <t>非暗属性、邪属性伤害减少；\n暗属性的特攻伤害无效；\n暗属性的技能耐性大幅增加。</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>非闇属性、邪属性ダメージ減少；\n闇属性の物攻ダメージを無効にする；\n邪属性のスキル耐性が大幅に増加する。</t>
+          <t>非暗属性、邪属性伤害减少；\n暗属性的物攻伤害无效；\n邪属性的技能耐性大幅增加。</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
